--- a/tools/config/item.xlsx
+++ b/tools/config/item.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="500"/>
+    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
     <sheet name="!Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">item!$I$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">item!$G$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,90 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">cd:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">配置格式
-{“类型”，“参数”},{“类型”，“参数”}
-类型=1，参数=系统id
-类型=2，参数=商店id
-类型=3,参数=礼包id
-类型=4,参数="语言表字段"
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="G5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">wilson:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1、普通物品
-2、宝箱物品（商店界面那个系统
-3、宝箱（背包使用，随机掉落，参数为dropid）
-4、自选
-5、终生卡体验卡
-10、代币
-11、角色属性类数值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">wilson:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>【1大类】
-101, 英雄觉醒材料, 英雄觉醒满级后，需要转为英雄尘
-102, 兵卡升级材料，兵卡满级后，需要转为兵尘
-103，宝具碎片（填了才能在图标右上角显示碎片
-【3大类】
-104：背包系统里使用，通过drop掉出到背包
-105：不需要点使用按钮，自动使用drop的
-106：自选
-107：终生体验卡，参数1是体验天数，参数2是已购买终生卡后再获得体验卡的转换道具</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -204,200 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t>不配置则无限制</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">admin:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>如果可使用，还可以配以下多种功能：
-1、可以批量使用
-2、获得时，自动弹出使用框
-（如果上面都没配，则没有上面的功能）</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t>大类</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="1"/>
-          </rPr>
-          <t>1</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="1"/>
-          </rPr>
-          <t>和</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="1"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="1"/>
-          </rPr>
-          <t>，填写</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">dropid
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="1"/>
-          </rPr>
-          <t>大类</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t>，填写</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">treasure_box_id
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">admin:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="1"/>
-          </rPr>
-          <t>大类</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="1"/>
-          </rPr>
-          <t>1+</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="1"/>
-          </rPr>
-          <t>小类</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="1"/>
-          </rPr>
-          <t>17</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="1"/>
-          </rPr>
-          <t>：每次使用需要使用多少个，才能执行一次对应的</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">dropid
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-大类4+小类106： 推荐道具序号</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O5" authorId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -409,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -497,19 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t>单位：分钟</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R5" authorId="0">
+    <comment ref="J5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -522,74 +234,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t>配表格式：货币类型</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t>,</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">数量
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">：兵尘
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <charset val="134"/>
-          </rPr>
-          <t>4</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK SC"/>
-            <charset val="134"/>
-          </rPr>
-          <t>：英雄</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="260">
   <si>
     <t>id</t>
   </si>
@@ -606,57 +256,21 @@
     <t>icon</t>
   </si>
   <si>
-    <t>getway</t>
-  </si>
-  <si>
-    <t>main_type</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
     <t>usable</t>
   </si>
   <si>
-    <t>use_on_sys</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>value1</t>
-  </si>
-  <si>
-    <t>value_rewards</t>
-  </si>
-  <si>
     <t>stacklimit</t>
   </si>
   <si>
     <t>quality</t>
   </si>
   <si>
-    <t>timelimit</t>
-  </si>
-  <si>
     <t>sort</t>
   </si>
   <si>
-    <t>maxlv_to_money</t>
-  </si>
-  <si>
-    <t>red_dots_cond</t>
-  </si>
-  <si>
-    <t>worth</t>
-  </si>
-  <si>
-    <t>test_json</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -669,15 +283,6 @@
     <t>text</t>
   </si>
   <si>
-    <t>table</t>
-  </si>
-  <si>
-    <t>comma</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
     <t>!mode</t>
   </si>
   <si>
@@ -696,85 +301,31 @@
     <t>道具描述</t>
   </si>
   <si>
-    <t>获取渠道</t>
-  </si>
-  <si>
-    <t>大类型</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
     <t>是否可使用</t>
   </si>
   <si>
-    <t>可使用时所需的系统</t>
-  </si>
-  <si>
-    <t>通用开关</t>
-  </si>
-  <si>
-    <t>类型参数1</t>
-  </si>
-  <si>
-    <t>类型参数2</t>
-  </si>
-  <si>
-    <t>类型参数3</t>
-  </si>
-  <si>
     <t>堆叠上限</t>
   </si>
   <si>
     <t>品质</t>
   </si>
   <si>
-    <t>超时时效</t>
-  </si>
-  <si>
     <t>排序依据</t>
   </si>
   <si>
-    <t>满级时自动转化为货币</t>
-  </si>
-  <si>
-    <t>红点显示所需系统解锁</t>
-  </si>
-  <si>
-    <t>价值量</t>
-  </si>
-  <si>
-    <t>测试json</t>
-  </si>
-  <si>
     <t>N随机兵卡（显示用，无实际功能</t>
   </si>
   <si>
-    <t>ui://common/armycard2</t>
-  </si>
-  <si>
-    <t>{"x":1,"y":2}</t>
-  </si>
-  <si>
     <t>R随机兵卡（显示用，无实际功能</t>
   </si>
   <si>
-    <t>ui://common/armycard3</t>
-  </si>
-  <si>
     <t>SR随机兵卡（显示用，无实际功能</t>
   </si>
   <si>
-    <t>ui://common/armycard4</t>
-  </si>
-  <si>
     <t>普池抽奖券</t>
-  </si>
-  <si>
-    <t>ui://common/itemIcon1004</t>
-  </si>
-  <si>
-    <t>{{"1","9"},{"1","3"},{"1","15"},{"3","1"},{"2","303"}}</t>
   </si>
   <si>
     <t>武僧英雄鸡C宝具碎片</t>
@@ -1481,7 +1032,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1679,16 +1230,6 @@
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Noto Sans CJK SC"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2236,7 +1777,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2261,21 +1802,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2285,31 +1817,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -2837,7 +2354,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.7666666666667" style="7" customWidth="1"/>
@@ -2845,484 +2362,280 @@
     <col min="3" max="3" width="15.5083333333333" style="7" customWidth="1"/>
     <col min="4" max="4" width="26.5" style="7" customWidth="1"/>
     <col min="5" max="5" width="11.875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="8.45833333333333" style="7" customWidth="1"/>
-    <col min="7" max="8" width="7.625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="12.0583333333333" style="7" customWidth="1"/>
-    <col min="10" max="10" width="7.54166666666667" style="7" customWidth="1"/>
-    <col min="11" max="11" width="7.625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="9.275" style="7" customWidth="1"/>
-    <col min="13" max="13" width="6.63333333333333" style="7" customWidth="1"/>
-    <col min="14" max="17" width="7.625" style="7" customWidth="1"/>
-    <col min="18" max="18" width="9" style="7"/>
-    <col min="19" max="19" width="7.375" style="8" customWidth="1"/>
-    <col min="20" max="20" width="16" style="7" customWidth="1"/>
-    <col min="21" max="21" width="9" style="9"/>
-    <col min="22" max="22" width="13.75" style="7" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="7"/>
+    <col min="6" max="6" width="7.625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.0583333333333" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10" style="7" customWidth="1"/>
+    <col min="9" max="9" width="7.5" style="7" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" spans="1:22">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
+    <row r="1" ht="17.25" spans="1:10">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+    </row>
+    <row r="2" ht="17.25" spans="1:10">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="C2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" spans="1:10">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="D3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="D4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="6" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="B5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="C5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="D5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="E5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="G5" s="16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" ht="17.25" spans="1:22">
-      <c r="A2" s="13" t="s">
+      <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="I5" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" spans="1:22">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14" t="s">
+      <c r="J5" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="14" t="s">
+    </row>
+    <row r="6" ht="17.25" spans="1:10">
+      <c r="A6" s="17">
+        <v>1001</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" s="12"/>
-      <c r="U3" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="V3" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="V4" s="9"/>
-    </row>
-    <row r="5" s="6" customFormat="1" ht="17.25" spans="1:22">
-      <c r="A5" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q5" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="R5" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="S5" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" ht="17.25" spans="1:22">
-      <c r="A6" s="25">
-        <v>1001</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="25" t="str">
+      <c r="C6" s="17" t="str">
         <f>"ItemName_"&amp;A6</f>
         <v>ItemName_1001</v>
       </c>
-      <c r="D6" s="25" t="str">
+      <c r="D6" s="17" t="str">
         <f>"ItemDesc_"&amp;A6</f>
         <v>ItemDesc_1001</v>
       </c>
-      <c r="E6" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25">
-        <v>1</v>
-      </c>
-      <c r="H6" s="25">
-        <v>0</v>
-      </c>
-      <c r="I6" s="25">
-        <v>0</v>
-      </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="O6" s="25">
-        <v>99999</v>
-      </c>
-      <c r="P6" s="7">
+      <c r="E6" s="17"/>
+      <c r="F6" s="17">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17">
+        <v>99999</v>
+      </c>
+      <c r="I6" s="7">
         <v>2</v>
       </c>
-      <c r="R6" s="7">
-        <v>0</v>
-      </c>
-      <c r="U6" s="9">
-        <v>20</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="25">
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="17">
         <v>1002</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="25" t="str">
+      <c r="B7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="17" t="str">
         <f>"ItemName_"&amp;A7</f>
         <v>ItemName_1002</v>
       </c>
-      <c r="D7" s="25" t="str">
+      <c r="D7" s="17" t="str">
         <f>"ItemDesc_"&amp;A7</f>
         <v>ItemDesc_1002</v>
       </c>
-      <c r="E7" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25">
-        <v>1</v>
-      </c>
-      <c r="H7" s="25">
-        <v>0</v>
-      </c>
-      <c r="I7" s="25">
-        <v>0</v>
-      </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="O7" s="25">
-        <v>99999</v>
-      </c>
-      <c r="P7" s="7">
+      <c r="E7" s="17"/>
+      <c r="F7" s="17">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17">
+        <v>99999</v>
+      </c>
+      <c r="I7" s="7">
         <v>3</v>
       </c>
-      <c r="R7" s="7">
-        <v>0</v>
-      </c>
-      <c r="U7" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="25">
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="17">
         <v>1003</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="25" t="str">
+      <c r="B8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="str">
         <f>"ItemName_"&amp;A8</f>
         <v>ItemName_1003</v>
       </c>
-      <c r="D8" s="25" t="str">
+      <c r="D8" s="17" t="str">
         <f>"ItemDesc_"&amp;A8</f>
         <v>ItemDesc_1003</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25">
-        <v>1</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0</v>
-      </c>
-      <c r="I8" s="25">
-        <v>0</v>
-      </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="O8" s="25">
-        <v>99999</v>
-      </c>
-      <c r="P8" s="7">
+      <c r="E8" s="17"/>
+      <c r="F8" s="17">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17">
+        <v>0</v>
+      </c>
+      <c r="H8" s="17">
+        <v>99999</v>
+      </c>
+      <c r="I8" s="7">
         <v>4</v>
       </c>
-      <c r="R8" s="7">
-        <v>0</v>
-      </c>
-      <c r="U8" s="9">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="25">
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="17">
         <v>1004</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="25" t="str">
+      <c r="B9" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="17" t="str">
         <f>"ItemName_"&amp;A9</f>
         <v>ItemName_1004</v>
       </c>
-      <c r="D9" s="25" t="str">
+      <c r="D9" s="17" t="str">
         <f>"ItemDesc_"&amp;A9</f>
         <v>ItemDesc_1004</v>
       </c>
-      <c r="E9" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="25">
-        <v>1</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0</v>
-      </c>
-      <c r="I9" s="25">
-        <v>0</v>
-      </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="O9" s="25">
-        <v>99999</v>
-      </c>
-      <c r="P9" s="7">
+      <c r="E9" s="17"/>
+      <c r="F9" s="17">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17">
+        <v>0</v>
+      </c>
+      <c r="H9" s="17">
+        <v>99999</v>
+      </c>
+      <c r="I9" s="7">
         <v>5</v>
       </c>
-      <c r="R9" s="7">
-        <v>0</v>
-      </c>
-      <c r="U9" s="9">
-        <v>800</v>
+      <c r="J9" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="I1:I9" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G9" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3350,16 +2663,16 @@
         <v>14001</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1">
         <v>1</v>
@@ -3380,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -3388,16 +2701,16 @@
         <v>14003</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G2" s="5">
         <v>1</v>
@@ -3418,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -3426,16 +2739,16 @@
         <v>14004</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -3456,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -3464,16 +2777,16 @@
         <v>14005</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -3494,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -3502,16 +2815,16 @@
         <v>14007</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -3532,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -3540,16 +2853,16 @@
         <v>14008</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -3570,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -3578,16 +2891,16 @@
         <v>14010</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -3608,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3616,16 +2929,16 @@
         <v>14011</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -3646,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -3654,16 +2967,16 @@
         <v>14013</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
@@ -3684,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3692,16 +3005,16 @@
         <v>14014</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
@@ -3722,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3730,16 +3043,16 @@
         <v>14015</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="G11" s="5">
         <v>1</v>
@@ -3760,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3768,16 +3081,16 @@
         <v>14016</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="G12" s="5">
         <v>1</v>
@@ -3798,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3806,16 +3119,16 @@
         <v>14017</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="G13" s="5">
         <v>1</v>
@@ -3836,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3844,16 +3157,16 @@
         <v>14018</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="G14" s="5">
         <v>1</v>
@@ -3874,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3882,16 +3195,16 @@
         <v>14019</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="G15" s="5">
         <v>1</v>
@@ -3912,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3920,16 +3233,16 @@
         <v>14020</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
@@ -3950,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3958,16 +3271,16 @@
         <v>14021</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="G17" s="5">
         <v>1</v>
@@ -3988,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3996,16 +3309,16 @@
         <v>14023</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G18" s="5">
         <v>1</v>
@@ -4026,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -4034,16 +3347,16 @@
         <v>14024</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="G19" s="5">
         <v>1</v>
@@ -4064,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -4072,16 +3385,16 @@
         <v>14025</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="G20" s="5">
         <v>1</v>
@@ -4102,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -4110,16 +3423,16 @@
         <v>14026</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="G21" s="5">
         <v>1</v>
@@ -4140,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -4148,16 +3461,16 @@
         <v>14027</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="G22" s="5">
         <v>1</v>
@@ -4178,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -4186,16 +3499,16 @@
         <v>14028</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G23" s="5">
         <v>1</v>
@@ -4216,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -4224,16 +3537,16 @@
         <v>14029</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="G24" s="5">
         <v>1</v>
@@ -4254,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -4262,16 +3575,16 @@
         <v>14030</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="G25" s="5">
         <v>1</v>
@@ -4292,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -4300,16 +3613,16 @@
         <v>14031</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="G26" s="5">
         <v>1</v>
@@ -4330,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -4338,16 +3651,16 @@
         <v>14035</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G27" s="5">
         <v>1</v>
@@ -4368,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -4376,16 +3689,16 @@
         <v>14036</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G28" s="5">
         <v>1</v>
@@ -4406,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4414,16 +3727,16 @@
         <v>14037</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="G29" s="5">
         <v>1</v>
@@ -4444,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -4452,16 +3765,16 @@
         <v>14038</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="G30" s="5">
         <v>1</v>
@@ -4482,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4490,16 +3803,16 @@
         <v>14039</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G31" s="5">
         <v>1</v>
@@ -4520,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4528,16 +3841,16 @@
         <v>14053</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G32" s="5">
         <v>1</v>
@@ -4558,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4566,16 +3879,16 @@
         <v>15001</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="G33" s="5">
         <v>1</v>
@@ -4596,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4604,16 +3917,16 @@
         <v>15002</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="G34" s="5">
         <v>1</v>
@@ -4634,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4642,16 +3955,16 @@
         <v>15003</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="G35" s="5">
         <v>1</v>
@@ -4672,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4680,16 +3993,16 @@
         <v>15004</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="G36" s="5">
         <v>1</v>
@@ -4710,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4718,16 +4031,16 @@
         <v>15009</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="G37" s="5">
         <v>1</v>
@@ -4748,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4756,16 +4069,16 @@
         <v>15010</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="G38" s="5">
         <v>1</v>
@@ -4786,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4794,16 +4107,16 @@
         <v>15011</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="G39" s="5">
         <v>1</v>
@@ -4824,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4832,16 +4145,16 @@
         <v>15012</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="G40" s="5">
         <v>1</v>
@@ -4862,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4870,16 +4183,16 @@
         <v>15015</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="D41" s="5" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="G41" s="5">
         <v>1</v>
@@ -4900,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4908,16 +4221,16 @@
         <v>15017</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="G42" s="5">
         <v>1</v>
@@ -4938,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4946,16 +4259,16 @@
         <v>15501</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="G43" s="5">
         <v>1</v>
@@ -4976,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4984,16 +4297,16 @@
         <v>15502</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="G44" s="5">
         <v>1</v>
@@ -5014,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -5022,16 +4335,16 @@
         <v>15503</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="G45" s="5">
         <v>1</v>
@@ -5052,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>264</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -5060,16 +4373,16 @@
         <v>15504</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="G46" s="5">
         <v>1</v>
@@ -5090,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -5098,16 +4411,16 @@
         <v>15507</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="G47" s="5">
         <v>1</v>
@@ -5128,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -5136,16 +4449,16 @@
         <v>15508</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="G48" s="5">
         <v>1</v>
@@ -5166,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -5174,16 +4487,16 @@
         <v>15509</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="G49" s="5">
         <v>1</v>
@@ -5204,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5212,16 +4525,16 @@
         <v>15512</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="G50" s="5">
         <v>1</v>
@@ -5242,7 +4555,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5250,16 +4563,16 @@
         <v>15513</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>285</v>
-      </c>
       <c r="D51" s="5" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="G51" s="5">
         <v>1</v>
@@ -5280,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="5" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5288,16 +4601,16 @@
         <v>15516</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="G52" s="5">
         <v>1</v>
@@ -5318,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" spans="1:16">

--- a/tools/config/item.xlsx
+++ b/tools/config/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="131">
   <si>
     <t>id</t>
   </si>
@@ -180,6 +180,246 @@
   </si>
   <si>
     <t>res://assets/icons/equit/musket.png</t>
+  </si>
+  <si>
+    <t>轻身</t>
+  </si>
+  <si>
+    <t>item.legend.roll_haste</t>
+  </si>
+  <si>
+    <t>item.legend.roll_haste.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_leather_boots.png</t>
+  </si>
+  <si>
+    <t>远滚</t>
+  </si>
+  <si>
+    <t>item.legend.roll_distance</t>
+  </si>
+  <si>
+    <t>item.legend.roll_distance.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_cloth_boots.png</t>
+  </si>
+  <si>
+    <t>幻影</t>
+  </si>
+  <si>
+    <t>item.legend.roll_phantom</t>
+  </si>
+  <si>
+    <t>item.legend.roll_phantom.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_mail_boots.png</t>
+  </si>
+  <si>
+    <t>滚势</t>
+  </si>
+  <si>
+    <t>item.legend.roll_momentum</t>
+  </si>
+  <si>
+    <t>item.legend.roll_momentum.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_plate_boots.png</t>
+  </si>
+  <si>
+    <t>残影</t>
+  </si>
+  <si>
+    <t>item.legend.roll_afterimage</t>
+  </si>
+  <si>
+    <t>item.legend.roll_afterimage.desc</t>
+  </si>
+  <si>
+    <t>影步</t>
+  </si>
+  <si>
+    <t>item.legend.shadow_step</t>
+  </si>
+  <si>
+    <t>item.legend.shadow_step.desc</t>
+  </si>
+  <si>
+    <t>凝气</t>
+  </si>
+  <si>
+    <t>item.legend.charge_focus</t>
+  </si>
+  <si>
+    <t>item.legend.charge_focus.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_cloth.png</t>
+  </si>
+  <si>
+    <t>蓄爆</t>
+  </si>
+  <si>
+    <t>item.legend.charge_power</t>
+  </si>
+  <si>
+    <t>item.legend.charge_power.desc</t>
+  </si>
+  <si>
+    <t>气浪</t>
+  </si>
+  <si>
+    <t>item.legend.charge_wave</t>
+  </si>
+  <si>
+    <t>item.legend.charge_wave.desc</t>
+  </si>
+  <si>
+    <t>行气</t>
+  </si>
+  <si>
+    <t>item.legend.charge_flow</t>
+  </si>
+  <si>
+    <t>item.legend.charge_flow.desc</t>
+  </si>
+  <si>
+    <t>不破</t>
+  </si>
+  <si>
+    <t>item.legend.charge_unbroken</t>
+  </si>
+  <si>
+    <t>item.legend.charge_unbroken.desc</t>
+  </si>
+  <si>
+    <t>原初 surge</t>
+  </si>
+  <si>
+    <t>item.legend.primal_surge</t>
+  </si>
+  <si>
+    <t>item.legend.primal_surge.desc</t>
+  </si>
+  <si>
+    <t>踏频</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_haste</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_haste.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_leather.png</t>
+  </si>
+  <si>
+    <t>裂地</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_crater</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_crater.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_mail.png</t>
+  </si>
+  <si>
+    <t>重踏</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_force</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_force.desc</t>
+  </si>
+  <si>
+    <t>res://assets/icons/equit/armor_plate.png</t>
+  </si>
+  <si>
+    <t>碎甲</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_sunder</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_sunder.desc</t>
+  </si>
+  <si>
+    <t>余震</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_quake</t>
+  </si>
+  <si>
+    <t>item.legend.stomp_quake.desc</t>
+  </si>
+  <si>
+    <t>泰坦踏</t>
+  </si>
+  <si>
+    <t>item.legend.titan_stomp</t>
+  </si>
+  <si>
+    <t>item.legend.titan_stomp.desc</t>
+  </si>
+  <si>
+    <t>从容</t>
+  </si>
+  <si>
+    <t>item.legend.parry_patience</t>
+  </si>
+  <si>
+    <t>item.legend.parry_patience.desc</t>
+  </si>
+  <si>
+    <t>还施</t>
+  </si>
+  <si>
+    <t>item.legend.parry_riposte</t>
+  </si>
+  <si>
+    <t>item.legend.parry_riposte.desc</t>
+  </si>
+  <si>
+    <t>锁敌</t>
+  </si>
+  <si>
+    <t>item.legend.parry_lock</t>
+  </si>
+  <si>
+    <t>item.legend.parry_lock.desc</t>
+  </si>
+  <si>
+    <t>收势</t>
+  </si>
+  <si>
+    <t>item.legend.parry_recovery</t>
+  </si>
+  <si>
+    <t>item.legend.parry_recovery.desc</t>
+  </si>
+  <si>
+    <t>宗师格</t>
+  </si>
+  <si>
+    <t>item.legend.parry_perfect_master</t>
+  </si>
+  <si>
+    <t>item.legend.parry_perfect_master.desc</t>
+  </si>
+  <si>
+    <t>神盾反击</t>
+  </si>
+  <si>
+    <t>item.legend.aegis_counter</t>
+  </si>
+  <si>
+    <t>item.legend.aegis_counter.desc</t>
   </si>
 </sst>
 </file>
@@ -192,7 +432,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,13 +450,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -366,7 +599,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,12 +645,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,148 +941,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1222,16 +1449,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="41.5" customWidth="1"/>
+    <col min="5" max="5" width="53.75" customWidth="1"/>
+    <col min="6" max="6" width="22.125" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="13.75" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
@@ -1440,7 +1668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="24" spans="1:16">
+    <row r="5" ht="74" customHeight="1" spans="1:16">
       <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
@@ -1676,6 +1904,1206 @@
       </c>
       <c r="P9">
         <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>2001</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0.15</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>2002</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.2</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>2003</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0.1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>2004</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0.05</v>
+      </c>
+      <c r="L13">
+        <v>0.18</v>
+      </c>
+      <c r="M13">
+        <v>0.05</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>2005</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0.12</v>
+      </c>
+      <c r="L14">
+        <v>0.12</v>
+      </c>
+      <c r="M14">
+        <v>0.08</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>2006</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0.25</v>
+      </c>
+      <c r="M15">
+        <v>0.1</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0.1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0.25</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0.05</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>2013</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0.18</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>2014</v>
+      </c>
+      <c r="B19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.08</v>
+      </c>
+      <c r="L19">
+        <v>0.12</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>2015</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>12</v>
+      </c>
+      <c r="K20">
+        <v>0.15</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0.3</v>
+      </c>
+      <c r="L21">
+        <v>-0.05</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
+      <c r="K22">
+        <v>0.08</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>8</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>2022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.12</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>10</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>2023</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>8</v>
+      </c>
+      <c r="K24">
+        <v>0.1</v>
+      </c>
+      <c r="L24">
+        <v>-0.05</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>12</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>2024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0.15</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0.05</v>
+      </c>
+      <c r="N25">
+        <v>6</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0.18</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>8</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>2026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>15</v>
+      </c>
+      <c r="K27">
+        <v>0.2</v>
+      </c>
+      <c r="L27">
+        <v>-0.08</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>15</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>2031</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0.08</v>
+      </c>
+      <c r="N28">
+        <v>10</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>2032</v>
+      </c>
+      <c r="B29" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0.2</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0.1</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>2033</v>
+      </c>
+      <c r="B30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
+      <c r="K30">
+        <v>0.12</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0.05</v>
+      </c>
+      <c r="N30">
+        <v>8</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>2034</v>
+      </c>
+      <c r="B31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0.05</v>
+      </c>
+      <c r="L31">
+        <v>0.08</v>
+      </c>
+      <c r="M31">
+        <v>0.12</v>
+      </c>
+      <c r="N31">
+        <v>6</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>2035</v>
+      </c>
+      <c r="B32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0.22</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.15</v>
+      </c>
+      <c r="N32">
+        <v>8</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>2036</v>
+      </c>
+      <c r="B33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>10</v>
+      </c>
+      <c r="K33">
+        <v>0.15</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>12</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
